--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\dodgeball\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD68A08D-B80B-4788-AC9C-3BF8947CC430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7FA525-84A5-4961-A11A-8EE47FC77FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10320" yWindow="3630" windowWidth="20890" windowHeight="13030" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="6490" yWindow="3680" windowWidth="20890" windowHeight="13030" activeTab="1" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
-    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId1"/>
+    <sheet name="ひな形" sheetId="3" r:id="rId1"/>
+    <sheet name="町内ドッジーズ" sheetId="4" r:id="rId2"/>
+    <sheet name="爆走ボーイズ" sheetId="5" r:id="rId3"/>
+    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="46">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -161,6 +164,74 @@
     <rPh sb="0" eb="3">
       <t>ダイテッキュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>たけし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こうた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まさる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゆうき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しんぺい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひろし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けんじ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>たかし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>たける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>りょうた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しょうた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゆうま</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はるき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だいき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けいた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しゅん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブーストシュート</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -524,6 +595,867 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F439D4-A850-4FB5-8C74-05CDC7D7499F}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>70</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>70</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>70</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>70</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0ECC56-C269-47E3-96D8-76D32031D01E}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EAEA44-C350-48E2-8358-D3E207C3C9E3}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>70</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>70</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>70</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10">
+        <v>70</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>6</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1F4421-BB84-4ED1-B973-A2EFCB49C642}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -581,16 +1513,16 @@
         <v>110</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J3" t="s">
         <v>24</v>
@@ -613,16 +1545,16 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
@@ -645,16 +1577,16 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J5" t="s">
         <v>26</v>
@@ -677,16 +1609,16 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" t="s">
         <v>27</v>
@@ -709,13 +1641,13 @@
         <v>110</v>
       </c>
       <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
         <v>8</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -741,16 +1673,16 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J8" t="s">
         <v>27</v>
@@ -773,16 +1705,16 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J9" t="s">
         <v>26</v>
@@ -805,16 +1737,16 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J10" t="s">
         <v>24</v>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\dodgeball\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7FA525-84A5-4961-A11A-8EE47FC77FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B662AEB1-94A1-4940-B350-DBC222862BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6490" yWindow="3680" windowWidth="20890" windowHeight="13030" activeTab="1" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
-    <sheet name="ひな形" sheetId="3" r:id="rId1"/>
-    <sheet name="町内ドッジーズ" sheetId="4" r:id="rId2"/>
-    <sheet name="爆走ボーイズ" sheetId="5" r:id="rId3"/>
-    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId4"/>
+    <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId1"/>
+    <sheet name="ひな形" sheetId="3" r:id="rId2"/>
+    <sheet name="町内ドッジーズ" sheetId="4" r:id="rId3"/>
+    <sheet name="爆走ボーイズ" sheetId="5" r:id="rId4"/>
+    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="54">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -232,6 +233,36 @@
   </si>
   <si>
     <t>ブーストシュート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブライアン</t>
+  </si>
+  <si>
+    <t>ジョー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マックス</t>
+  </si>
+  <si>
+    <t>スティーブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブロック</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -595,6 +626,285 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5613FED0-80B4-43A0-9E24-89A1AE1FAA43}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>70</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>70</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>70</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>70</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F439D4-A850-4FB5-8C74-05CDC7D7499F}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -849,7 +1159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0ECC56-C269-47E3-96D8-76D32031D01E}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -1152,7 +1462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EAEA44-C350-48E2-8358-D3E207C3C9E3}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -1455,7 +1765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1F4421-BB84-4ED1-B973-A2EFCB49C642}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\dodgeball\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B662AEB1-94A1-4940-B350-DBC222862BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB3884F-66E0-4AC7-9685-BDF93ABC03A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="55">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -263,6 +263,10 @@
   </si>
   <si>
     <t>ブロック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トリプルショット</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -673,26 +677,29 @@
       <c r="B3" t="s">
         <v>12</v>
       </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
       <c r="D3">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E3">
         <v>100</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -702,26 +709,29 @@
       <c r="B4" t="s">
         <v>12</v>
       </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
       <c r="D4">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -731,26 +741,29 @@
       <c r="B5" t="s">
         <v>12</v>
       </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
       <c r="D5">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -760,26 +773,29 @@
       <c r="B6" t="s">
         <v>12</v>
       </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
       <c r="D6">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -789,26 +805,29 @@
       <c r="B7" t="s">
         <v>12</v>
       </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
       <c r="D7">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="E7">
         <v>100</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -818,23 +837,26 @@
       <c r="B8" t="s">
         <v>13</v>
       </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
       <c r="D8">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="E8">
         <v>100</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J8" t="s">
         <v>25</v>
@@ -847,26 +869,29 @@
       <c r="B9" t="s">
         <v>13</v>
       </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
       <c r="D9">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -876,26 +901,29 @@
       <c r="B10" t="s">
         <v>13</v>
       </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
       <c r="D10">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="E10">
         <v>100</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce66247190394c0c/Desktop/dodgeball/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{4DB3884F-66E0-4AC7-9685-BDF93ABC03A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C620230-79B0-4A30-92F1-5B2F062D17F6}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{4DB3884F-66E0-4AC7-9685-BDF93ABC03A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E5E2C31-2CF4-412C-B850-4C973835A796}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="1170" windowWidth="22600" windowHeight="16910" activeTab="3" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="680" yWindow="1850" windowWidth="22600" windowHeight="16910" activeTab="5" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
     <sheet name="ひな形" sheetId="3" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="爆走ボーイズ" sheetId="5" r:id="rId3"/>
     <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId4"/>
     <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId5"/>
+    <sheet name="ドスコイズ" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="64">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -267,6 +268,45 @@
   </si>
   <si>
     <t>トリプルショット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>らいのふじ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はりておう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>がんさい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ごうのやま</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だいふんか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かいりきやま</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ちゃんこまる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>張りてシュート</t>
+    <rPh sb="0" eb="1">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よこづな</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -332,6 +372,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2094,4 +2138,308 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5060B0-BD2F-4B59-8A6D-38B1FDE5FBE7}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="16.58203125" customWidth="1"/>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>280</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>170</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>170</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>170</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>170</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>170</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>170</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>170</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -5,20 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce66247190394c0c/Desktop/dodgeball/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\dodgeball\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{4DB3884F-66E0-4AC7-9685-BDF93ABC03A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E5E2C31-2CF4-412C-B850-4C973835A796}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABE4C8C-1203-4079-B30F-E4A34A230E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="1850" windowWidth="22600" windowHeight="16910" activeTab="5" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" activeTab="1" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
-    <sheet name="ひな形" sheetId="3" r:id="rId1"/>
-    <sheet name="町内ドッジーズ" sheetId="4" r:id="rId2"/>
-    <sheet name="爆走ボーイズ" sheetId="5" r:id="rId3"/>
-    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId4"/>
-    <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId5"/>
-    <sheet name="ドスコイズ" sheetId="7" r:id="rId6"/>
+    <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
+    <sheet name="レッドファイアーズ" sheetId="9" r:id="rId2"/>
+    <sheet name="ひな形" sheetId="3" r:id="rId3"/>
+    <sheet name="町内ドッジーズ" sheetId="4" r:id="rId4"/>
+    <sheet name="爆走ボーイズ" sheetId="5" r:id="rId5"/>
+    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId6"/>
+    <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId7"/>
+    <sheet name="ドスコイズ" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="80">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -307,6 +309,70 @@
   </si>
   <si>
     <t>よこづな</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あお</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブルー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーシャン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そら</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こおり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぐんじょう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しんく</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もみじ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>れっか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほむら</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぐれん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>べに</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かえん</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -379,9 +445,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -419,7 +485,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -525,7 +591,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -667,13 +733,379 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7344F31-2055-4A8B-991B-C5E189E5A373}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>60</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{927028B5-675B-4D19-B72B-1C735406FCAC}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>60</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F439D4-A850-4FB5-8C74-05CDC7D7499F}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -928,7 +1360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0ECC56-C269-47E3-96D8-76D32031D01E}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -1231,7 +1663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EAEA44-C350-48E2-8358-D3E207C3C9E3}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -1534,7 +1966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1F4421-BB84-4ED1-B973-A2EFCB49C642}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -1837,7 +2269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5613FED0-80B4-43A0-9E24-89A1AE1FAA43}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -2140,7 +2572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5060B0-BD2F-4B59-8A6D-38B1FDE5FBE7}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\dodgeball\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABE4C8C-1203-4079-B30F-E4A34A230E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5501B9-D46C-4F5C-928D-E8BB363AB2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" activeTab="1" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="ひな形" sheetId="3" r:id="rId3"/>
     <sheet name="町内ドッジーズ" sheetId="4" r:id="rId4"/>
     <sheet name="爆走ボーイズ" sheetId="5" r:id="rId5"/>
-    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId6"/>
-    <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId7"/>
-    <sheet name="ドスコイズ" sheetId="7" r:id="rId8"/>
+    <sheet name="ドスコイズ" sheetId="7" r:id="rId6"/>
+    <sheet name="くいだおレンジャーズ" sheetId="10" r:id="rId7"/>
+    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId8"/>
+    <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="89">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -373,6 +374,48 @@
   </si>
   <si>
     <t>かえん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>たこへい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おこのみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くしかつ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つうてん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なんでや</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まいど</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くいだおれ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どうとん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通天閣落とし</t>
+    <rPh sb="0" eb="3">
+      <t>ツウテンカク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1967,612 +2010,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1F4421-BB84-4ED1-B973-A2EFCB49C642}">
-  <dimension ref="A2:J10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="2" max="3" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="67.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3">
-        <v>150</v>
-      </c>
-      <c r="E3">
-        <v>110</v>
-      </c>
-      <c r="F3">
-        <v>8</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <v>9</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4">
-        <v>150</v>
-      </c>
-      <c r="E4">
-        <v>110</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4">
-        <v>9</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>150</v>
-      </c>
-      <c r="E5">
-        <v>110</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>150</v>
-      </c>
-      <c r="E6">
-        <v>110</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>250</v>
-      </c>
-      <c r="E7">
-        <v>150</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>150</v>
-      </c>
-      <c r="E8">
-        <v>110</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>9</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9">
-        <v>150</v>
-      </c>
-      <c r="E9">
-        <v>110</v>
-      </c>
-      <c r="F9">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>8</v>
-      </c>
-      <c r="H9">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <v>7</v>
-      </c>
-      <c r="J9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10">
-        <v>150</v>
-      </c>
-      <c r="E10">
-        <v>110</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="G10">
-        <v>11</v>
-      </c>
-      <c r="H10">
-        <v>9</v>
-      </c>
-      <c r="I10">
-        <v>7</v>
-      </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5613FED0-80B4-43A0-9E24-89A1AE1FAA43}">
-  <dimension ref="A2:J10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="2" max="3" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="67.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3">
-        <v>140</v>
-      </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>12</v>
-      </c>
-      <c r="H3">
-        <v>13</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>140</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4">
-        <v>8</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>320</v>
-      </c>
-      <c r="E5">
-        <v>150</v>
-      </c>
-      <c r="F5">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>140</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>150</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>150</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
-      </c>
-      <c r="H8">
-        <v>9</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9">
-        <v>140</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>7</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>7</v>
-      </c>
-      <c r="J9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10">
-        <v>130</v>
-      </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-      <c r="H10">
-        <v>13</v>
-      </c>
-      <c r="I10">
-        <v>8</v>
-      </c>
-      <c r="J10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5060B0-BD2F-4B59-8A6D-38B1FDE5FBE7}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -2874,4 +2311,914 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B02B2E-3221-441F-BC4D-4458503A8B6C}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>180</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>120</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>120</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>120</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>120</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>120</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>120</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>120</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1F4421-BB84-4ED1-B973-A2EFCB49C642}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>150</v>
+      </c>
+      <c r="E3">
+        <v>110</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <v>110</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>150</v>
+      </c>
+      <c r="E5">
+        <v>110</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>150</v>
+      </c>
+      <c r="E6">
+        <v>110</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>250</v>
+      </c>
+      <c r="E7">
+        <v>150</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>150</v>
+      </c>
+      <c r="E8">
+        <v>110</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>150</v>
+      </c>
+      <c r="E9">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10">
+        <v>150</v>
+      </c>
+      <c r="E10">
+        <v>110</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <v>9</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5613FED0-80B4-43A0-9E24-89A1AE1FAA43}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>140</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>13</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>140</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>320</v>
+      </c>
+      <c r="E5">
+        <v>150</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>140</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>150</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>150</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>140</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>130</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>13</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\dodgeball\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce66247190394c0c/Desktop/dodgeball/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5501B9-D46C-4F5C-928D-E8BB363AB2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{8D5501B9-D46C-4F5C-928D-E8BB363AB2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C2E6663-E235-4A4B-B5A4-502C9DEF5845}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="680" yWindow="1850" windowWidth="22600" windowHeight="16910" firstSheet="4" activeTab="8" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="町内ドッジーズ" sheetId="4" r:id="rId4"/>
     <sheet name="爆走ボーイズ" sheetId="5" r:id="rId5"/>
     <sheet name="ドスコイズ" sheetId="7" r:id="rId6"/>
-    <sheet name="くいだおレンジャーズ" sheetId="10" r:id="rId7"/>
-    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId8"/>
-    <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId9"/>
+    <sheet name="アイアンガーズ" sheetId="11" r:id="rId7"/>
+    <sheet name="くいだおレンジャーズ" sheetId="10" r:id="rId8"/>
+    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId9"/>
+    <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="97">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -143,10 +144,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ブースト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>稲妻</t>
     <rPh sb="0" eb="2">
       <t>イナズマ</t>
@@ -154,10 +151,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>バナナ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>稲妻</t>
     <rPh sb="0" eb="2">
       <t>イナヅマ</t>
@@ -386,10 +379,6 @@
   </si>
   <si>
     <t>くしかつ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>つうてん</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -416,6 +405,53 @@
     <rPh sb="3" eb="4">
       <t>オ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おおきに</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気合ストレート</t>
+    <rPh sb="0" eb="2">
+      <t>キアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シュナイダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミュラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クライン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベッカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホフマン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リヒター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ケラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィッシャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライトニング</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -488,9 +524,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -528,7 +564,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -634,7 +670,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -776,7 +812,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -825,7 +861,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -842,7 +878,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -859,7 +895,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -876,7 +912,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -893,7 +929,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -910,7 +946,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -927,7 +963,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -944,7 +980,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -957,6 +993,309 @@
       </c>
       <c r="E10">
         <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5613FED0-80B4-43A0-9E24-89A1AE1FAA43}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>140</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>13</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>140</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>320</v>
+      </c>
+      <c r="E5">
+        <v>150</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>140</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>150</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>150</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>140</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>130</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>13</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1008,7 +1347,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1025,7 +1364,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1042,7 +1381,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -1059,7 +1398,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -1076,7 +1415,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1093,7 +1432,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1110,7 +1449,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1127,7 +1466,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1212,7 +1551,7 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1238,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1264,7 +1603,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1290,7 +1629,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1316,7 +1655,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1342,7 +1681,7 @@
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1368,7 +1707,7 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1394,7 +1733,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1446,7 +1785,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1473,12 +1812,12 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1505,12 +1844,12 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -1519,30 +1858,30 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E5">
         <v>100</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -1569,12 +1908,12 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1601,12 +1940,12 @@
         <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1633,12 +1972,12 @@
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1665,12 +2004,12 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1697,7 +2036,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +2088,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1776,12 +2115,12 @@
         <v>6</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1808,12 +2147,12 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -1822,30 +2161,30 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>100</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -1872,12 +2211,12 @@
         <v>6</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1904,12 +2243,12 @@
         <v>6</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1936,12 +2275,12 @@
         <v>6</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1968,12 +2307,12 @@
         <v>6</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2000,7 +2339,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2053,7 +2392,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -2080,12 +2419,12 @@
         <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -2112,12 +2451,12 @@
         <v>7</v>
       </c>
       <c r="J4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -2144,12 +2483,12 @@
         <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -2176,12 +2515,12 @@
         <v>7</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -2208,12 +2547,12 @@
         <v>7</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2240,12 +2579,12 @@
         <v>7</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2272,12 +2611,12 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2304,7 +2643,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2314,6 +2653,309 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E458C94-BAB3-4266-858F-1341BF567CF1}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>270</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>140</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>140</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>140</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>140</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>140</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>140</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>140</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B02B2E-3221-441F-BC4D-4458503A8B6C}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -2357,7 +2999,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -2384,12 +3026,12 @@
         <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -2416,12 +3058,12 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -2448,12 +3090,12 @@
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -2480,12 +3122,12 @@
         <v>7</v>
       </c>
       <c r="J6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -2512,12 +3154,12 @@
         <v>7</v>
       </c>
       <c r="J7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2544,12 +3186,12 @@
         <v>6</v>
       </c>
       <c r="J8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2576,12 +3218,12 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2608,7 +3250,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2617,7 +3259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1F4421-BB84-4ED1-B973-A2EFCB49C642}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -2687,7 +3329,7 @@
         <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2719,7 +3361,7 @@
         <v>8</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2751,7 +3393,7 @@
         <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2783,7 +3425,7 @@
         <v>8</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2815,7 +3457,7 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2847,7 +3489,7 @@
         <v>7</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2879,7 +3521,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2911,310 +3553,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5613FED0-80B4-43A0-9E24-89A1AE1FAA43}">
-  <dimension ref="A2:J10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="2" max="3" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="67.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3">
-        <v>140</v>
-      </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>12</v>
-      </c>
-      <c r="H3">
-        <v>13</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>140</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4">
-        <v>8</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>320</v>
-      </c>
-      <c r="E5">
-        <v>150</v>
-      </c>
-      <c r="F5">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>140</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>150</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>150</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
-      </c>
-      <c r="H8">
-        <v>9</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9">
-        <v>140</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>7</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>7</v>
-      </c>
-      <c r="J9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10">
-        <v>130</v>
-      </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-      <c r="H10">
-        <v>13</v>
-      </c>
-      <c r="I10">
-        <v>8</v>
-      </c>
-      <c r="J10" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce66247190394c0c/Desktop/dodgeball/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\dodgeball\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{8D5501B9-D46C-4F5C-928D-E8BB363AB2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C2E6663-E235-4A4B-B5A4-502C9DEF5845}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431BFD7D-52FF-4E45-B7F3-D6BCD4758B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="1850" windowWidth="22600" windowHeight="16910" firstSheet="4" activeTab="8" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="4" activeTab="6" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
@@ -524,9 +524,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -564,7 +564,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -670,7 +670,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -812,7 +812,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2754,7 +2754,7 @@
         <v>7</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2786,7 +2786,7 @@
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2818,7 +2818,7 @@
         <v>7</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2850,7 +2850,7 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2882,7 +2882,7 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2914,7 +2914,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2946,7 +2946,7 @@
         <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\dodgeball\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce66247190394c0c/Desktop/dodgeball/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431BFD7D-52FF-4E45-B7F3-D6BCD4758B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{431BFD7D-52FF-4E45-B7F3-D6BCD4758B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF3C3A5A-E525-4FFA-814F-7B00D81BBF59}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="4" activeTab="6" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="1020" yWindow="2190" windowWidth="22600" windowHeight="16910" firstSheet="4" activeTab="8" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="98">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -452,6 +452,10 @@
   </si>
   <si>
     <t>ライトニング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バナナシュート</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -519,14 +523,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -564,7 +564,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -670,7 +670,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -812,7 +812,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3393,7 +3393,7 @@
         <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce66247190394c0c/Desktop/dodgeball/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{431BFD7D-52FF-4E45-B7F3-D6BCD4758B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF3C3A5A-E525-4FFA-814F-7B00D81BBF59}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{431BFD7D-52FF-4E45-B7F3-D6BCD4758B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753CE898-3226-427C-83C2-0611E5740D5B}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="2190" windowWidth="22600" windowHeight="16910" firstSheet="4" activeTab="8" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="1360" yWindow="2530" windowWidth="31210" windowHeight="16990" firstSheet="2" activeTab="10" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="くいだおレンジャーズ" sheetId="10" r:id="rId8"/>
     <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId9"/>
     <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId10"/>
+    <sheet name="ゼンマイギアーズ" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="106">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -456,6 +457,38 @@
   </si>
   <si>
     <t>バナナシュート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゼロ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボルト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピストン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>センサー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レーダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コイル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビット</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -521,6 +554,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1304,6 +1341,285 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B483C03-5920-431E-BB24-E56AF96271DE}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="67.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>320</v>
+      </c>
+      <c r="E3">
+        <v>200</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>220</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>220</v>
+      </c>
+      <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>220</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>220</v>
+      </c>
+      <c r="E7">
+        <v>200</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>220</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>9</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>220</v>
+      </c>
+      <c r="E9">
+        <v>200</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>9</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>220</v>
+      </c>
+      <c r="E10">
+        <v>200</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>7</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{927028B5-675B-4D19-B72B-1C735406FCAC}">
   <dimension ref="A2:J10"/>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce66247190394c0c/Desktop/dodgeball/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{431BFD7D-52FF-4E45-B7F3-D6BCD4758B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753CE898-3226-427C-83C2-0611E5740D5B}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{431BFD7D-52FF-4E45-B7F3-D6BCD4758B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE33911-5D11-434A-9989-8652008609BF}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="2530" windowWidth="31210" windowHeight="16990" firstSheet="2" activeTab="10" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="1970" yWindow="3150" windowWidth="31210" windowHeight="16990" firstSheet="2" activeTab="10" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="108">
   <si>
     <t>れつ</t>
     <phoneticPr fontId="1"/>
@@ -489,6 +489,14 @@
   </si>
   <si>
     <t>ビット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンロケット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クロックストップ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1396,7 +1404,7 @@
         <v>200</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -1405,10 +1413,10 @@
         <v>8</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1419,13 +1427,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E4">
         <v>200</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>7</v>
@@ -1434,10 +1442,10 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1448,13 +1456,13 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <v>200</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -1463,10 +1471,10 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1477,13 +1485,13 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E6">
         <v>200</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>7</v>
@@ -1492,10 +1500,10 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1506,13 +1514,13 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E7">
         <v>200</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -1521,10 +1529,10 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1535,13 +1543,13 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E8">
         <v>200</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -1550,10 +1558,10 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1564,13 +1572,13 @@
         <v>13</v>
       </c>
       <c r="D9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E9">
         <v>200</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>7</v>
@@ -1579,10 +1587,10 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1593,13 +1601,13 @@
         <v>13</v>
       </c>
       <c r="D10">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>7</v>
@@ -1608,10 +1616,10 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce66247190394c0c/Desktop/dodgeball/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\newdodge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{431BFD7D-52FF-4E45-B7F3-D6BCD4758B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE33911-5D11-434A-9989-8652008609BF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8986C98E-569C-4485-BF0D-2F4EE583DA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1970" yWindow="3150" windowWidth="31210" windowHeight="16990" firstSheet="2" activeTab="10" xr2:uid="{D69C31E5-6DE1-4DCA-A8B0-9AD24F880A47}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
@@ -24,509 +24,418 @@
     <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId9"/>
     <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId10"/>
     <sheet name="ゼンマイギアーズ" sheetId="12" r:id="rId11"/>
+    <sheet name="ギャラクタコーズ" sheetId="13" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="118">
+  <si>
+    <t>名前</t>
+  </si>
+  <si>
+    <t>ポジション</t>
+  </si>
+  <si>
+    <t>タイプ</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>スタミナ</t>
+  </si>
+  <si>
+    <t>パワー</t>
+  </si>
+  <si>
+    <t>スピード</t>
+  </si>
+  <si>
+    <t>ジャンプ</t>
+  </si>
+  <si>
+    <t>テクニック</t>
+  </si>
+  <si>
+    <t>特殊シュート</t>
+  </si>
+  <si>
+    <t>あお</t>
+  </si>
+  <si>
+    <t>内野</t>
+  </si>
+  <si>
+    <t>ノーマル</t>
+  </si>
+  <si>
+    <t>ぐんじょう</t>
+  </si>
+  <si>
+    <t>こおり</t>
+  </si>
+  <si>
+    <t>うみ</t>
+  </si>
+  <si>
+    <t>そら</t>
+  </si>
+  <si>
+    <t>ブルー</t>
+  </si>
+  <si>
+    <t>外野</t>
+  </si>
+  <si>
+    <t>アクア</t>
+  </si>
+  <si>
+    <t>オーシャン</t>
+  </si>
+  <si>
+    <t>あか</t>
+  </si>
+  <si>
+    <t>しんく</t>
+  </si>
+  <si>
+    <t>もみじ</t>
+  </si>
+  <si>
+    <t>れっか</t>
+  </si>
+  <si>
+    <t>ほむら</t>
+  </si>
+  <si>
+    <t>ぐれん</t>
+  </si>
+  <si>
+    <t>べに</t>
+  </si>
+  <si>
+    <t>かえん</t>
+  </si>
+  <si>
+    <t>稲妻</t>
+  </si>
+  <si>
+    <t>たけし</t>
+  </si>
+  <si>
+    <t>気合ストレート</t>
+  </si>
+  <si>
+    <t>こうた</t>
+  </si>
+  <si>
+    <t>まさる</t>
+  </si>
+  <si>
+    <t>ゆうき</t>
+  </si>
+  <si>
+    <t>しんぺい</t>
+  </si>
+  <si>
+    <t>ひろし</t>
+  </si>
+  <si>
+    <t>けんじ</t>
+  </si>
+  <si>
+    <t>たかし</t>
+  </si>
+  <si>
+    <t>たける</t>
+  </si>
+  <si>
+    <t>ちび</t>
+  </si>
+  <si>
+    <t>りょうた</t>
+  </si>
+  <si>
+    <t>しょうた</t>
+  </si>
+  <si>
+    <t>ブーストシュート</t>
+  </si>
+  <si>
+    <t>ゆうま</t>
+  </si>
+  <si>
+    <t>はるき</t>
+  </si>
+  <si>
+    <t>だいき</t>
+  </si>
+  <si>
+    <t>けいた</t>
+  </si>
+  <si>
+    <t>しゅん</t>
+  </si>
+  <si>
+    <t>よこづな</t>
+  </si>
+  <si>
+    <t>デーブ</t>
+  </si>
+  <si>
+    <t>張りてシュート</t>
+  </si>
+  <si>
+    <t>らいのふじ</t>
+  </si>
+  <si>
+    <t>はりておう</t>
+  </si>
+  <si>
+    <t>がんさい</t>
+  </si>
+  <si>
+    <t>ごうのやま</t>
+  </si>
+  <si>
+    <t>だいふんか</t>
+  </si>
+  <si>
+    <t>かいりきやま</t>
+  </si>
+  <si>
+    <t>ちゃんこまる</t>
+  </si>
+  <si>
+    <t>シュナイダー</t>
+  </si>
+  <si>
+    <t>大鉄球</t>
+  </si>
+  <si>
+    <t>ミュラー</t>
+  </si>
+  <si>
+    <t>クライン</t>
+  </si>
+  <si>
+    <t>ベッカー</t>
+  </si>
+  <si>
+    <t>ホフマン</t>
+  </si>
+  <si>
+    <t>リヒター</t>
+  </si>
+  <si>
+    <t>ケラー</t>
+  </si>
+  <si>
+    <t>フィッシャー</t>
+  </si>
+  <si>
+    <t>たこへい</t>
+  </si>
+  <si>
+    <t>通天閣落とし</t>
+  </si>
+  <si>
+    <t>おこのみ</t>
+  </si>
+  <si>
+    <t>くしかつ</t>
+  </si>
+  <si>
+    <t>くいだおれ</t>
+  </si>
+  <si>
+    <t>おおきに</t>
+  </si>
+  <si>
+    <t>なんでや</t>
+  </si>
+  <si>
+    <t>まいど</t>
+  </si>
+  <si>
+    <t>どうとん</t>
+  </si>
   <si>
     <t>れつ</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>むさし</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>しょう</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>のっぽ</t>
+  </si>
+  <si>
+    <t>バナナシュート</t>
   </si>
   <si>
     <t>じん</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>だいち</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライトニング</t>
   </si>
   <si>
     <t>はやと</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>えんじ</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ひかる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名前</t>
-    <rPh sb="0" eb="2">
-      <t>ナマエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HP</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スタミナ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ポジション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>内野</t>
-    <rPh sb="0" eb="2">
-      <t>ナイヤ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>外野</t>
-    <rPh sb="0" eb="2">
-      <t>ガイヤ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パワー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スピード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャンプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テクニック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デーブ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ノーマル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>のっぽ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ちび</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特殊シュート</t>
-    <rPh sb="0" eb="2">
-      <t>トクシュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>稲妻</t>
-    <rPh sb="0" eb="2">
-      <t>イナズマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>稲妻</t>
-    <rPh sb="0" eb="2">
-      <t>イナヅマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>大鉄球</t>
-    <rPh sb="0" eb="3">
-      <t>ダイテッキュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>たけし</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>こうた</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まさる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゆうき</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しんぺい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ひろし</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>けんじ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>たかし</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>たける</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>りょうた</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しょうた</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゆうま</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>はるき</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>だいき</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>けいた</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しゅん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ブーストシュート</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>トム</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ブライアン</t>
   </si>
   <si>
     <t>ジョー</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トリプルショット</t>
   </si>
   <si>
     <t>ニック</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>マックス</t>
   </si>
   <si>
     <t>スティーブ</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>レックス</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ブロック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>トリプルショット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>らいのふじ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>はりておう</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>がんさい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ごうのやま</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>だいふんか</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>かいりきやま</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ちゃんこまる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>張りてシュート</t>
-    <rPh sb="0" eb="1">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>よこづな</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あお</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ブルー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オーシャン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>うみ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そら</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>こおり</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ぐんじょう</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アクア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あか</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しんく</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>もみじ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>れっか</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ほむら</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ぐれん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>べに</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>かえん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>たこへい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>おこのみ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>くしかつ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>なんでや</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まいど</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>くいだおれ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>どうとん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>通天閣落とし</t>
-    <rPh sb="0" eb="3">
-      <t>ツウテンカク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>おおきに</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>気合ストレート</t>
-    <rPh sb="0" eb="2">
-      <t>キアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シュナイダー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ミュラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>クライン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベッカー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ホフマン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リヒター</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ケラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フィッシャー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ライトニング</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>バナナシュート</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ゼロ</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンロケット</t>
   </si>
   <si>
     <t>ボルト</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クロックストップ</t>
   </si>
   <si>
     <t>ギア</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ピストン</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>センサー</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>レーダー</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>コイル</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ビット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ロックオンロケット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>クロックストップ</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギャラクタコーズ</t>
+  </si>
+  <si>
+    <t>オクト</t>
+  </si>
+  <si>
+    <t>宇宙人</t>
+  </si>
+  <si>
+    <t>UFOスピン</t>
+  </si>
+  <si>
+    <t>ピコ</t>
+  </si>
+  <si>
+    <t>グニャ</t>
+  </si>
+  <si>
+    <t>フワン</t>
+  </si>
+  <si>
+    <t>キュル</t>
+  </si>
+  <si>
+    <t>ポル</t>
+  </si>
+  <si>
+    <t>ニュル</t>
+  </si>
+  <si>
+    <t>モニョ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF123C4B"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF167F9D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CFFCB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -543,8 +452,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -562,10 +480,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -609,110 +523,16 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office 2013 - 2022">
@@ -724,23 +544,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -750,23 +570,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -774,26 +594,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -828,17 +645,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -855,16 +672,11 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7344F31-2055-4A8B-991B-C5E189E5A373}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -874,45 +686,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -923,13 +735,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -940,13 +752,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -957,13 +769,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -974,13 +786,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>60</v>
@@ -991,13 +803,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>60</v>
@@ -1008,13 +820,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -1025,13 +837,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>60</v>
@@ -1041,13 +853,13 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5613FED0-80B4-43A0-9E24-89A1AE1FAA43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1057,45 +869,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D3">
         <v>140</v>
@@ -1116,18 +928,18 @@
         <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>140</v>
@@ -1148,18 +960,18 @@
         <v>7</v>
       </c>
       <c r="J4" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>320</v>
@@ -1180,18 +992,18 @@
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>140</v>
@@ -1212,18 +1024,18 @@
         <v>8</v>
       </c>
       <c r="J6" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>150</v>
@@ -1244,18 +1056,18 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>150</v>
@@ -1276,18 +1088,18 @@
         <v>7</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
       </c>
       <c r="D9">
         <v>140</v>
@@ -1308,18 +1120,18 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <v>130</v>
@@ -1340,17 +1152,17 @@
         <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B483C03-5920-431E-BB24-E56AF96271DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1360,42 +1172,42 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>320</v>
@@ -1416,7 +1228,7 @@
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1424,7 +1236,7 @@
         <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>200</v>
@@ -1445,15 +1257,15 @@
         <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>200</v>
@@ -1474,15 +1286,15 @@
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>200</v>
@@ -1503,15 +1315,15 @@
         <v>11</v>
       </c>
       <c r="J6" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>200</v>
@@ -1532,15 +1344,15 @@
         <v>11</v>
       </c>
       <c r="J7" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>200</v>
@@ -1561,15 +1373,15 @@
         <v>11</v>
       </c>
       <c r="J8" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>200</v>
@@ -1590,15 +1402,15 @@
         <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D10">
         <v>200</v>
@@ -1619,17 +1431,340 @@
         <v>11</v>
       </c>
       <c r="J10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="13.4140625" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.9140625" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="3">
+        <v>350</v>
+      </c>
+      <c r="E3" s="3">
+        <v>130</v>
+      </c>
+      <c r="F3" s="3">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3">
+        <v>8</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="3">
+        <v>250</v>
+      </c>
+      <c r="E4" s="3">
+        <v>115</v>
+      </c>
+      <c r="F4" s="3">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3">
+        <v>16</v>
+      </c>
+      <c r="I4" s="3">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="3">
+        <v>250</v>
+      </c>
+      <c r="E5" s="3">
+        <v>115</v>
+      </c>
+      <c r="F5" s="3">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="3">
+        <v>250</v>
+      </c>
+      <c r="E6" s="3">
+        <v>120</v>
+      </c>
+      <c r="F6" s="3">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3">
+        <v>12</v>
+      </c>
+      <c r="J6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="3">
+        <v>250</v>
+      </c>
+      <c r="E7" s="3">
+        <v>115</v>
+      </c>
+      <c r="F7" s="3">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3">
+        <v>8</v>
+      </c>
+      <c r="H7" s="3">
+        <v>16</v>
+      </c>
+      <c r="I7" s="3">
+        <v>12</v>
+      </c>
+      <c r="J7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="3">
+        <v>250</v>
+      </c>
+      <c r="E8" s="3">
+        <v>115</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3">
+        <v>7</v>
+      </c>
+      <c r="H8" s="3">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>12</v>
+      </c>
+      <c r="J8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="3">
+        <v>250</v>
+      </c>
+      <c r="E9" s="3">
+        <v>120</v>
+      </c>
+      <c r="F9" s="3">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3">
+        <v>12</v>
+      </c>
+      <c r="J9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="3">
+        <v>250</v>
+      </c>
+      <c r="E10" s="3">
+        <v>115</v>
+      </c>
+      <c r="F10" s="3">
+        <v>9</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6</v>
+      </c>
+      <c r="H10" s="3">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
+        <v>12</v>
+      </c>
+      <c r="J10" t="s">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{927028B5-675B-4D19-B72B-1C735406FCAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1639,45 +1774,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -1688,13 +1823,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -1705,13 +1840,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1722,13 +1857,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -1739,13 +1874,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>60</v>
@@ -1756,13 +1891,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>60</v>
@@ -1773,13 +1908,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -1790,13 +1925,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>60</v>
@@ -1806,13 +1941,13 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F439D4-A850-4FB5-8C74-05CDC7D7499F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1822,39 +1957,39 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>70</v>
@@ -1875,12 +2010,12 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>70</v>
@@ -1901,12 +2036,12 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>70</v>
@@ -1927,12 +2062,12 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>70</v>
@@ -1953,12 +2088,12 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>70</v>
@@ -1979,12 +2114,12 @@
         <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>70</v>
@@ -2005,12 +2140,12 @@
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>70</v>
@@ -2031,12 +2166,12 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -2057,17 +2192,17 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0ECC56-C269-47E3-96D8-76D32031D01E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2077,45 +2212,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>50</v>
@@ -2136,18 +2271,18 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -2168,18 +2303,18 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -2200,18 +2335,18 @@
         <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -2232,18 +2367,18 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>50</v>
@@ -2264,18 +2399,18 @@
         <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -2296,18 +2431,18 @@
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>50</v>
@@ -2328,18 +2463,18 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -2360,17 +2495,17 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EAEA44-C350-48E2-8358-D3E207C3C9E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2380,45 +2515,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>70</v>
@@ -2439,18 +2574,18 @@
         <v>6</v>
       </c>
       <c r="J3" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>70</v>
@@ -2471,18 +2606,18 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>110</v>
@@ -2508,13 +2643,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>70</v>
@@ -2535,18 +2670,18 @@
         <v>6</v>
       </c>
       <c r="J6" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>70</v>
@@ -2567,18 +2702,18 @@
         <v>6</v>
       </c>
       <c r="J7" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>40</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
       </c>
       <c r="D8">
         <v>70</v>
@@ -2599,18 +2734,18 @@
         <v>6</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>70</v>
@@ -2631,18 +2766,18 @@
         <v>6</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -2663,17 +2798,17 @@
         <v>6</v>
       </c>
       <c r="J10" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5060B0-BD2F-4B59-8A6D-38B1FDE5FBE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2684,45 +2819,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D3">
         <v>280</v>
@@ -2743,18 +2878,18 @@
         <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>170</v>
@@ -2775,18 +2910,18 @@
         <v>7</v>
       </c>
       <c r="J4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D5">
         <v>170</v>
@@ -2807,18 +2942,18 @@
         <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>170</v>
@@ -2839,18 +2974,18 @@
         <v>7</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>170</v>
@@ -2871,18 +3006,18 @@
         <v>7</v>
       </c>
       <c r="J7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>170</v>
@@ -2903,18 +3038,18 @@
         <v>7</v>
       </c>
       <c r="J8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>170</v>
@@ -2935,18 +3070,18 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>170</v>
@@ -2967,17 +3102,17 @@
         <v>6</v>
       </c>
       <c r="J10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E458C94-BAB3-4266-858F-1341BF567CF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2987,45 +3122,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>270</v>
@@ -3046,18 +3181,18 @@
         <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>140</v>
@@ -3078,18 +3213,18 @@
         <v>7</v>
       </c>
       <c r="J4" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>140</v>
@@ -3110,18 +3245,18 @@
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>140</v>
@@ -3142,18 +3277,18 @@
         <v>7</v>
       </c>
       <c r="J6" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>140</v>
@@ -3174,18 +3309,18 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>140</v>
@@ -3206,18 +3341,18 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>140</v>
@@ -3238,18 +3373,18 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>140</v>
@@ -3270,17 +3405,17 @@
         <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B02B2E-3221-441F-BC4D-4458503A8B6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -3291,45 +3426,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>180</v>
@@ -3350,18 +3485,18 @@
         <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>120</v>
@@ -3382,18 +3517,18 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>120</v>
@@ -3414,18 +3549,18 @@
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>120</v>
@@ -3446,18 +3581,18 @@
         <v>7</v>
       </c>
       <c r="J6" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>120</v>
@@ -3478,18 +3613,18 @@
         <v>7</v>
       </c>
       <c r="J7" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>120</v>
@@ -3510,18 +3645,18 @@
         <v>6</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>120</v>
@@ -3542,18 +3677,18 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>120</v>
@@ -3574,17 +3709,17 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1F4421-BB84-4ED1-B973-A2EFCB49C642}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -3594,45 +3729,45 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>150</v>
@@ -3653,18 +3788,18 @@
         <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>150</v>
@@ -3685,18 +3820,18 @@
         <v>8</v>
       </c>
       <c r="J4" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D5">
         <v>150</v>
@@ -3717,18 +3852,18 @@
         <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>150</v>
@@ -3749,18 +3884,18 @@
         <v>8</v>
       </c>
       <c r="J6" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>250</v>
@@ -3781,18 +3916,18 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>150</v>
@@ -3813,18 +3948,18 @@
         <v>7</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>150</v>
@@ -3845,18 +3980,18 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <v>150</v>
@@ -3877,11 +4012,11 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\newdodge\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\Github\newdodge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8986C98E-569C-4485-BF0D-2F4EE583DA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C859DF86-C910-4797-8831-61A09BCECCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1970" yWindow="3150" windowWidth="31210" windowHeight="16990" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
@@ -20,18 +20,19 @@
     <sheet name="爆走ボーイズ" sheetId="5" r:id="rId5"/>
     <sheet name="ドスコイズ" sheetId="7" r:id="rId6"/>
     <sheet name="アイアンガーズ" sheetId="11" r:id="rId7"/>
-    <sheet name="くいだおレンジャーズ" sheetId="10" r:id="rId8"/>
-    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId9"/>
+    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId8"/>
+    <sheet name="くいだおレンジャーズ" sheetId="10" r:id="rId9"/>
     <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId10"/>
     <sheet name="ゼンマイギアーズ" sheetId="12" r:id="rId11"/>
-    <sheet name="ギャラクタコーズ" sheetId="13" r:id="rId12"/>
+    <sheet name="アークマーズ" sheetId="14" r:id="rId12"/>
+    <sheet name="ギャラクタコーズ" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="135">
   <si>
     <t>名前</t>
   </si>
@@ -237,6 +238,39 @@
     <t>フィッシャー</t>
   </si>
   <si>
+    <t>れつ</t>
+  </si>
+  <si>
+    <t>むさし</t>
+  </si>
+  <si>
+    <t>しょう</t>
+  </si>
+  <si>
+    <t>のっぽ</t>
+  </si>
+  <si>
+    <t>バナナシュート</t>
+  </si>
+  <si>
+    <t>じん</t>
+  </si>
+  <si>
+    <t>だいち</t>
+  </si>
+  <si>
+    <t>ライトニング</t>
+  </si>
+  <si>
+    <t>はやと</t>
+  </si>
+  <si>
+    <t>えんじ</t>
+  </si>
+  <si>
+    <t>ひかる</t>
+  </si>
+  <si>
     <t>たこへい</t>
   </si>
   <si>
@@ -264,39 +298,6 @@
     <t>どうとん</t>
   </si>
   <si>
-    <t>れつ</t>
-  </si>
-  <si>
-    <t>むさし</t>
-  </si>
-  <si>
-    <t>しょう</t>
-  </si>
-  <si>
-    <t>のっぽ</t>
-  </si>
-  <si>
-    <t>バナナシュート</t>
-  </si>
-  <si>
-    <t>じん</t>
-  </si>
-  <si>
-    <t>だいち</t>
-  </si>
-  <si>
-    <t>ライトニング</t>
-  </si>
-  <si>
-    <t>はやと</t>
-  </si>
-  <si>
-    <t>えんじ</t>
-  </si>
-  <si>
-    <t>ひかる</t>
-  </si>
-  <si>
     <t>トム</t>
   </si>
   <si>
@@ -385,13 +386,65 @@
   </si>
   <si>
     <t>モニョ</t>
+  </si>
+  <si>
+    <t>大魔王アークマ</t>
+  </si>
+  <si>
+    <t>魔王</t>
+  </si>
+  <si>
+    <t>ヘルファイア</t>
+  </si>
+  <si>
+    <t>溶岩ゴーレム</t>
+  </si>
+  <si>
+    <t>メテオクラッシュ</t>
+  </si>
+  <si>
+    <t>吸血鬼ヴァルド</t>
+  </si>
+  <si>
+    <t>吸血鬼</t>
+  </si>
+  <si>
+    <t>ブラッドドレイン</t>
+  </si>
+  <si>
+    <t>シールドデビル</t>
+  </si>
+  <si>
+    <t>盾悪魔</t>
+  </si>
+  <si>
+    <t>デビルシールド</t>
+  </si>
+  <si>
+    <t>ノクス</t>
+  </si>
+  <si>
+    <t>ミニデビル</t>
+  </si>
+  <si>
+    <t>デビルトライアングル連携</t>
+  </si>
+  <si>
+    <t>ペコ</t>
+  </si>
+  <si>
+    <t>ポコ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">溶岩ゴーレム </t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,6 +472,21 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF231833"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -438,12 +506,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -452,7 +535,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -463,6 +546,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -907,7 +1002,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>140</v>
@@ -1131,7 +1226,7 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D10">
         <v>130</v>
@@ -1442,6 +1537,318 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="10.08203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="19.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="6">
+        <v>500</v>
+      </c>
+      <c r="E3" s="6">
+        <v>200</v>
+      </c>
+      <c r="F3" s="6">
+        <v>18</v>
+      </c>
+      <c r="G3" s="6">
+        <v>13</v>
+      </c>
+      <c r="H3" s="6">
+        <v>13</v>
+      </c>
+      <c r="I3" s="6">
+        <v>13</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="6">
+        <v>350</v>
+      </c>
+      <c r="E4" s="6">
+        <v>150</v>
+      </c>
+      <c r="F4" s="6">
+        <v>16</v>
+      </c>
+      <c r="G4" s="6">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6">
+        <v>4</v>
+      </c>
+      <c r="I4" s="6">
+        <v>9</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="6">
+        <v>270</v>
+      </c>
+      <c r="E5" s="6">
+        <v>150</v>
+      </c>
+      <c r="F5" s="6">
+        <v>11</v>
+      </c>
+      <c r="G5" s="6">
+        <v>11</v>
+      </c>
+      <c r="H5" s="6">
+        <v>9</v>
+      </c>
+      <c r="I5" s="6">
+        <v>12</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="6">
+        <v>280</v>
+      </c>
+      <c r="E6" s="6">
+        <v>150</v>
+      </c>
+      <c r="F6" s="6">
+        <v>8</v>
+      </c>
+      <c r="G6" s="6">
+        <v>12</v>
+      </c>
+      <c r="H6" s="6">
+        <v>8</v>
+      </c>
+      <c r="I6" s="6">
+        <v>14</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6">
+        <v>120</v>
+      </c>
+      <c r="E7" s="6">
+        <v>100</v>
+      </c>
+      <c r="F7" s="6">
+        <v>7</v>
+      </c>
+      <c r="G7" s="6">
+        <v>7</v>
+      </c>
+      <c r="H7" s="6">
+        <v>7</v>
+      </c>
+      <c r="I7" s="6">
+        <v>7</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="6">
+        <v>130</v>
+      </c>
+      <c r="E8" s="6">
+        <v>135</v>
+      </c>
+      <c r="F8" s="6">
+        <v>9</v>
+      </c>
+      <c r="G8" s="6">
+        <v>13</v>
+      </c>
+      <c r="H8" s="6">
+        <v>13</v>
+      </c>
+      <c r="I8" s="6">
+        <v>12</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="6">
+        <v>130</v>
+      </c>
+      <c r="E9" s="6">
+        <v>135</v>
+      </c>
+      <c r="F9" s="6">
+        <v>9</v>
+      </c>
+      <c r="G9" s="6">
+        <v>13</v>
+      </c>
+      <c r="H9" s="6">
+        <v>13</v>
+      </c>
+      <c r="I9" s="6">
+        <v>12</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="6">
+        <v>130</v>
+      </c>
+      <c r="E10" s="6">
+        <v>135</v>
+      </c>
+      <c r="F10" s="6">
+        <v>9</v>
+      </c>
+      <c r="G10" s="6">
+        <v>13</v>
+      </c>
+      <c r="H10" s="6">
+        <v>13</v>
+      </c>
+      <c r="I10" s="6">
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -3419,7 +3826,6 @@
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="12.33203125" customWidth="1"/>
     <col min="10" max="10" width="67.5" customWidth="1"/>
   </cols>
@@ -3467,30 +3873,30 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H3">
         <v>9</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -3499,22 +3905,22 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J4" t="s">
         <v>31</v>
@@ -3522,39 +3928,39 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
       <c r="D5">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>8</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -3563,22 +3969,22 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="s">
         <v>31</v>
@@ -3586,39 +3992,39 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7">
         <v>9</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
@@ -3627,22 +4033,22 @@
         <v>12</v>
       </c>
       <c r="D8">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
@@ -3650,28 +4056,28 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="D9">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -3682,28 +4088,28 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F10">
         <v>8</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -3723,6 +4129,7 @@
   <dimension ref="A2:J10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="12.33203125" customWidth="1"/>
     <col min="10" max="10" width="67.5" customWidth="1"/>
   </cols>
@@ -3761,7 +4168,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -3770,30 +4177,30 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>9</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -3802,22 +4209,22 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J4" t="s">
         <v>31</v>
@@ -3825,39 +4232,39 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>8</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -3866,22 +4273,22 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J6" t="s">
         <v>31</v>
@@ -3889,34 +4296,34 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>9</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -3930,22 +4337,22 @@
         <v>12</v>
       </c>
       <c r="D8">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
@@ -3959,22 +4366,22 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -3991,22 +4398,22 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>8</v>
       </c>
       <c r="G10">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>7</v>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,32 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\Github\newdodge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80E3733-DE3E-4624-A615-361D73284F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCC8591-66F2-43A9-AD3A-33A39F28F3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ブルースターズ" sheetId="8" r:id="rId1"/>
-    <sheet name="レッドファイアーズ" sheetId="9" r:id="rId2"/>
+    <sheet name="ブルースターズ" sheetId="1" r:id="rId1"/>
+    <sheet name="レッドファイアーズ" sheetId="2" r:id="rId2"/>
     <sheet name="ひな形" sheetId="3" r:id="rId3"/>
     <sheet name="町内ドッジーズ" sheetId="4" r:id="rId4"/>
     <sheet name="爆走ボーイズ" sheetId="5" r:id="rId5"/>
-    <sheet name="ドスコイズ" sheetId="7" r:id="rId6"/>
-    <sheet name="アイアンガーズ" sheetId="11" r:id="rId7"/>
-    <sheet name="日の丸ボンバーズ" sheetId="1" r:id="rId8"/>
-    <sheet name="くいだおレンジャーズ" sheetId="10" r:id="rId9"/>
-    <sheet name="アメリカンビッグボールズ" sheetId="6" r:id="rId10"/>
-    <sheet name="ゼンマイギアーズ" sheetId="12" r:id="rId11"/>
-    <sheet name="アークマーズ" sheetId="14" r:id="rId12"/>
+    <sheet name="ドスコイズ" sheetId="6" r:id="rId6"/>
+    <sheet name="アイアンガーズ" sheetId="7" r:id="rId7"/>
+    <sheet name="日の丸ボンバーズ" sheetId="8" r:id="rId8"/>
+    <sheet name="くいだおレンジャーズ" sheetId="9" r:id="rId9"/>
+    <sheet name="アメリカンビッグボールズ" sheetId="10" r:id="rId10"/>
+    <sheet name="ゼンマイギアーズ" sheetId="11" r:id="rId11"/>
+    <sheet name="アークマーズ" sheetId="12" r:id="rId12"/>
     <sheet name="ギャラクタコーズ" sheetId="13" r:id="rId13"/>
-    <sheet name="ブレイバーズ" sheetId="15" r:id="rId14"/>
+    <sheet name="ブレイバーズ" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="0" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="162">
   <si>
     <t>名前</t>
   </si>
@@ -71,15 +71,90 @@
     <t>特殊シュート</t>
   </si>
   <si>
+    <t>勇者</t>
+  </si>
+  <si>
+    <t>内野 固定</t>
+  </si>
+  <si>
+    <t>ノーマル</t>
+  </si>
+  <si>
+    <t>ブレイブスラッシュ</t>
+  </si>
+  <si>
+    <t>戦士</t>
+  </si>
+  <si>
+    <t>内野 2</t>
+  </si>
+  <si>
+    <t>ギガブレイク</t>
+  </si>
+  <si>
+    <t>魔法使い</t>
+  </si>
+  <si>
+    <t>内野 3</t>
+  </si>
+  <si>
+    <t>魔法</t>
+  </si>
+  <si>
+    <t>ルナティックミラージュ</t>
+  </si>
+  <si>
+    <t>聖騎士</t>
+  </si>
+  <si>
+    <t>内野 4</t>
+  </si>
+  <si>
+    <t>シャイニングアロー</t>
+  </si>
+  <si>
+    <t>僧侶</t>
+  </si>
+  <si>
+    <t>内野 5</t>
+  </si>
+  <si>
+    <t>グランドヒール</t>
+  </si>
+  <si>
+    <t>弓使い</t>
+  </si>
+  <si>
+    <t>外野 1</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>武闘家</t>
+  </si>
+  <si>
+    <t>外野 2</t>
+  </si>
+  <si>
+    <t>百裂ラッシュ</t>
+  </si>
+  <si>
+    <t>吟遊詩人</t>
+  </si>
+  <si>
+    <t>外野 3</t>
+  </si>
+  <si>
+    <t>勝利の行進曲</t>
+  </si>
+  <si>
     <t>あお</t>
   </si>
   <si>
     <t>内野</t>
   </si>
   <si>
-    <t>ノーマル</t>
-  </si>
-  <si>
     <t>ぐんじょう</t>
   </si>
   <si>
@@ -362,6 +437,63 @@
     <t>ビット</t>
   </si>
   <si>
+    <t>大魔王アークマ</t>
+  </si>
+  <si>
+    <t>魔王</t>
+  </si>
+  <si>
+    <t>ヘルファイア</t>
+  </si>
+  <si>
+    <t>溶岩ゴーレム</t>
+  </si>
+  <si>
+    <t>メテオクラッシュ</t>
+  </si>
+  <si>
+    <t>吸血鬼ヴァルド</t>
+  </si>
+  <si>
+    <t>吸血鬼</t>
+  </si>
+  <si>
+    <t>ブラッドドレイン</t>
+  </si>
+  <si>
+    <t>シールドデビル</t>
+  </si>
+  <si>
+    <t>盾悪魔</t>
+  </si>
+  <si>
+    <t>デビルシールド</t>
+  </si>
+  <si>
+    <t>魔女メルティ</t>
+  </si>
+  <si>
+    <t>魔女</t>
+  </si>
+  <si>
+    <t>アルカナスフィア</t>
+  </si>
+  <si>
+    <t>ピコ</t>
+  </si>
+  <si>
+    <t>ミニデビル</t>
+  </si>
+  <si>
+    <t>デビルトライアングル連携</t>
+  </si>
+  <si>
+    <t>ペコ</t>
+  </si>
+  <si>
+    <t>ポコ</t>
+  </si>
+  <si>
     <t>オクト</t>
   </si>
   <si>
@@ -371,9 +503,6 @@
     <t>UFOスピン</t>
   </si>
   <si>
-    <t>ピコ</t>
-  </si>
-  <si>
     <t>グニャ</t>
   </si>
   <si>
@@ -390,111 +519,6 @@
   </si>
   <si>
     <t>モニョ</t>
-  </si>
-  <si>
-    <t>勇者</t>
-  </si>
-  <si>
-    <t>内野 固定</t>
-  </si>
-  <si>
-    <t>戦士</t>
-  </si>
-  <si>
-    <t>内野 2</t>
-  </si>
-  <si>
-    <t>魔法使い</t>
-  </si>
-  <si>
-    <t>内野 3</t>
-  </si>
-  <si>
-    <t>魔法</t>
-  </si>
-  <si>
-    <t>聖騎士</t>
-  </si>
-  <si>
-    <t>内野 4</t>
-  </si>
-  <si>
-    <t>僧侶</t>
-  </si>
-  <si>
-    <t>内野 5</t>
-  </si>
-  <si>
-    <t>弓使い</t>
-  </si>
-  <si>
-    <t>外野 1</t>
-  </si>
-  <si>
-    <t>武闘家</t>
-  </si>
-  <si>
-    <t>外野 2</t>
-  </si>
-  <si>
-    <t>吟遊詩人</t>
-  </si>
-  <si>
-    <t>外野 3</t>
-  </si>
-  <si>
-    <t>大魔王アークマ</t>
-  </si>
-  <si>
-    <t>魔王</t>
-  </si>
-  <si>
-    <t>ヘルファイア</t>
-  </si>
-  <si>
-    <t>溶岩ゴーレム</t>
-  </si>
-  <si>
-    <t>メテオクラッシュ</t>
-  </si>
-  <si>
-    <t>吸血鬼ヴァルド</t>
-  </si>
-  <si>
-    <t>吸血鬼</t>
-  </si>
-  <si>
-    <t>ブラッドドレイン</t>
-  </si>
-  <si>
-    <t>シールドデビル</t>
-  </si>
-  <si>
-    <t>盾悪魔</t>
-  </si>
-  <si>
-    <t>デビルシールド</t>
-  </si>
-  <si>
-    <t>魔女メルティ</t>
-  </si>
-  <si>
-    <t>魔女</t>
-  </si>
-  <si>
-    <t>アルカナスフィア</t>
-  </si>
-  <si>
-    <t>ミニデビル</t>
-  </si>
-  <si>
-    <t>デビルトライアングル連携</t>
-  </si>
-  <si>
-    <t>ペコ</t>
-  </si>
-  <si>
-    <t>ポコ</t>
   </si>
 </sst>
 </file>
@@ -559,7 +583,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -572,6 +596,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -787,17 +812,17 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="2.9140625" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="19.08203125" customWidth="1"/>
-    <col min="12" max="12" width="10.25" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7" style="4" customWidth="1"/>
+    <col min="4" max="4" width="2.9140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.08203125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="10.25" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -840,10 +865,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -868,10 +893,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -896,10 +921,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -924,10 +949,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -952,10 +977,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -980,10 +1005,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -1008,10 +1033,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
@@ -1036,10 +1061,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
@@ -1073,17 +1098,17 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="3.25" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7" style="4" customWidth="1"/>
+    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1126,13 +1151,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2">
         <v>140</v>
@@ -1159,18 +1184,18 @@
         <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D4" s="2">
         <v>140</v>
@@ -1197,15 +1222,15 @@
         <v>9</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -1235,15 +1260,15 @@
         <v>13</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -1273,18 +1298,18 @@
         <v>9</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D7" s="2">
         <v>150</v>
@@ -1311,15 +1336,15 @@
         <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -1349,18 +1374,18 @@
         <v>9</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2">
         <v>140</v>
@@ -1387,18 +1412,18 @@
         <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="D10" s="2">
         <v>130</v>
@@ -1425,7 +1450,7 @@
         <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1439,18 +1464,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="3.25" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="15.08203125" customWidth="1"/>
+    <col min="1" max="1" width="7" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.08203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1493,10 +1518,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2">
@@ -1524,15 +1549,15 @@
         <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="2">
@@ -1542,7 +1567,7 @@
         <v>200</v>
       </c>
       <c r="F4" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="2">
         <v>7</v>
@@ -1560,15 +1585,15 @@
         <v>7</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2">
@@ -1578,7 +1603,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2">
         <v>7</v>
@@ -1596,15 +1621,15 @@
         <v>7</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2">
@@ -1614,7 +1639,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="2">
         <v>7</v>
@@ -1632,15 +1657,15 @@
         <v>7</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="2">
@@ -1650,7 +1675,7 @@
         <v>200</v>
       </c>
       <c r="F7" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" s="2">
         <v>7</v>
@@ -1668,15 +1693,15 @@
         <v>7</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2">
@@ -1686,7 +1711,7 @@
         <v>200</v>
       </c>
       <c r="F8" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="2">
         <v>7</v>
@@ -1704,15 +1729,15 @@
         <v>7</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2">
@@ -1722,7 +1747,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="2">
         <v>7</v>
@@ -1740,15 +1765,15 @@
         <v>7</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2">
@@ -1758,7 +1783,7 @@
         <v>200</v>
       </c>
       <c r="F10" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="2">
         <v>7</v>
@@ -1776,7 +1801,7 @@
         <v>7</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1790,18 +1815,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.9140625" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="10.08203125" customWidth="1"/>
-    <col min="4" max="4" width="3.25" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="19.75" customWidth="1"/>
+    <col min="1" max="1" width="11.9140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.08203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="19.75" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1844,13 +1869,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D3" s="2">
         <v>500</v>
@@ -1877,18 +1902,18 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D4" s="2">
         <v>350</v>
@@ -1915,18 +1940,18 @@
         <v>6</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D5" s="2">
         <v>270</v>
@@ -1953,18 +1978,18 @@
         <v>7</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D6" s="2">
         <v>280</v>
@@ -1991,18 +2016,18 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D7" s="2">
         <v>250</v>
@@ -2029,18 +2054,18 @@
         <v>8</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D8" s="2">
         <v>130</v>
@@ -2067,18 +2092,18 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D9" s="2">
         <v>130</v>
@@ -2105,18 +2130,18 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" s="2">
         <v>130</v>
@@ -2143,7 +2168,7 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2157,18 +2182,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="3.25" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="10.25" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="10.25" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -2211,13 +2236,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D3" s="2">
         <v>350</v>
@@ -2238,24 +2263,24 @@
         <v>15</v>
       </c>
       <c r="J3" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D4" s="2">
         <v>250</v>
@@ -2276,24 +2301,24 @@
         <v>12</v>
       </c>
       <c r="J4" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D5" s="2">
         <v>250</v>
@@ -2314,24 +2339,24 @@
         <v>12</v>
       </c>
       <c r="J5" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D6" s="2">
         <v>250</v>
@@ -2352,24 +2377,24 @@
         <v>12</v>
       </c>
       <c r="J6" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D7" s="2">
         <v>250</v>
@@ -2390,24 +2415,24 @@
         <v>12</v>
       </c>
       <c r="J7" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D8" s="2">
         <v>250</v>
@@ -2428,24 +2453,24 @@
         <v>12</v>
       </c>
       <c r="J8" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D9" s="2">
         <v>250</v>
@@ -2466,24 +2491,24 @@
         <v>12</v>
       </c>
       <c r="J9" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D10" s="2">
         <v>250</v>
@@ -2504,13 +2529,13 @@
         <v>12</v>
       </c>
       <c r="J10" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K10" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2524,18 +2549,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="9.5" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="11.9140625" customWidth="1"/>
+    <col min="1" max="1" width="7" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="6.9140625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.9140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -2578,10 +2603,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -2605,21 +2630,21 @@
         <v>13</v>
       </c>
       <c r="J3" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K3" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -2631,7 +2656,7 @@
         <v>115</v>
       </c>
       <c r="F4" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="2">
         <v>7</v>
@@ -2640,27 +2665,27 @@
         <v>7</v>
       </c>
       <c r="I4" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2">
         <v>250</v>
@@ -2669,39 +2694,39 @@
         <v>150</v>
       </c>
       <c r="F5" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2">
         <v>8</v>
       </c>
       <c r="H5" s="2">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2">
         <v>10</v>
       </c>
-      <c r="I5" s="2">
-        <v>13</v>
-      </c>
       <c r="J5" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" s="2">
         <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="E6" s="2">
         <v>140</v>
@@ -2716,30 +2741,30 @@
         <v>9</v>
       </c>
       <c r="I6" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J6" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K6" s="2">
         <v>7</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="E7" s="2">
         <v>150</v>
@@ -2754,24 +2779,24 @@
         <v>8</v>
       </c>
       <c r="I7" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J7" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K7" s="2">
         <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
@@ -2783,39 +2808,39 @@
         <v>135</v>
       </c>
       <c r="F8" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="2">
         <v>12</v>
       </c>
       <c r="H8" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" s="2">
         <v>13</v>
       </c>
       <c r="J8" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="E9" s="2">
         <v>135</v>
@@ -2824,36 +2849,36 @@
         <v>12</v>
       </c>
       <c r="G9" s="2">
+        <v>18</v>
+      </c>
+      <c r="H9" s="2">
+        <v>18</v>
+      </c>
+      <c r="I9" s="2">
         <v>15</v>
       </c>
-      <c r="H9" s="2">
-        <v>15</v>
-      </c>
-      <c r="I9" s="2">
-        <v>13</v>
-      </c>
       <c r="J9" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K9" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="2">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="E10" s="2">
         <v>145</v>
@@ -2865,19 +2890,19 @@
         <v>11</v>
       </c>
       <c r="H10" s="2">
+        <v>8</v>
+      </c>
+      <c r="I10" s="2">
         <v>10</v>
       </c>
-      <c r="I10" s="2">
-        <v>14</v>
-      </c>
       <c r="J10" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K10" s="2">
         <v>11</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2891,18 +2916,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="2.9140625" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="10.25" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7" style="4" customWidth="1"/>
+    <col min="4" max="4" width="2.9140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="10.25" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -2945,10 +2970,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -2973,10 +2998,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -3001,10 +3026,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -3029,10 +3054,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -3057,10 +3082,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -3085,10 +3110,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -3113,10 +3138,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
@@ -3141,10 +3166,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
@@ -3178,18 +3203,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="3.75" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="2.9140625" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="10.25" customWidth="1"/>
+    <col min="1" max="1" width="3.75" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="2.9140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="10.25" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -3233,7 +3258,7 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2">
@@ -3261,13 +3286,13 @@
         <v>5</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="2">
@@ -3295,13 +3320,13 @@
         <v>5</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2">
@@ -3329,13 +3354,13 @@
         <v>5</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2">
@@ -3363,13 +3388,13 @@
         <v>5</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="2">
@@ -3397,13 +3422,13 @@
         <v>5</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2">
@@ -3431,13 +3456,13 @@
         <v>5</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2">
@@ -3465,13 +3490,13 @@
         <v>5</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2">
@@ -3499,7 +3524,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3513,18 +3538,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="2.9140625" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="11.9140625" customWidth="1"/>
+    <col min="1" max="1" width="7" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7" style="4" customWidth="1"/>
+    <col min="4" max="4" width="2.9140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.9140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -3567,10 +3592,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -3600,15 +3625,15 @@
         <v>5</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -3638,15 +3663,15 @@
         <v>5</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -3676,15 +3701,15 @@
         <v>5</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -3714,15 +3739,15 @@
         <v>5</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -3752,15 +3777,15 @@
         <v>5</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -3790,15 +3815,15 @@
         <v>5</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
@@ -3828,15 +3853,15 @@
         <v>5</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
@@ -3866,7 +3891,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3880,18 +3905,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="3.25" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="13.4140625" customWidth="1"/>
+    <col min="1" max="1" width="7" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="13.4140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -3934,13 +3959,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D3" s="2">
         <v>70</v>
@@ -3967,18 +3992,18 @@
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2">
         <v>70</v>
@@ -4005,18 +4030,18 @@
         <v>6</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2">
         <v>110</v>
@@ -4043,18 +4068,18 @@
         <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D6" s="2">
         <v>70</v>
@@ -4081,18 +4106,18 @@
         <v>6</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D7" s="2">
         <v>70</v>
@@ -4119,18 +4144,18 @@
         <v>6</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2">
         <v>70</v>
@@ -4157,18 +4182,18 @@
         <v>6</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D9" s="2">
         <v>70</v>
@@ -4195,18 +4220,18 @@
         <v>6</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2">
         <v>70</v>
@@ -4233,7 +4258,7 @@
         <v>6</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4247,18 +4272,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.25" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="11.9140625" customWidth="1"/>
+    <col min="1" max="1" width="10.25" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.9140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -4301,13 +4326,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D3" s="2">
         <v>280</v>
@@ -4334,18 +4359,18 @@
         <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D4" s="2">
         <v>170</v>
@@ -4372,18 +4397,18 @@
         <v>6</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2">
         <v>170</v>
@@ -4410,18 +4435,18 @@
         <v>6</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2">
         <v>170</v>
@@ -4448,18 +4473,18 @@
         <v>6</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2">
         <v>170</v>
@@ -4486,18 +4511,18 @@
         <v>6</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2">
         <v>170</v>
@@ -4524,18 +4549,18 @@
         <v>6</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2">
         <v>170</v>
@@ -4562,18 +4587,18 @@
         <v>6</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D10" s="2">
         <v>170</v>
@@ -4600,7 +4625,7 @@
         <v>6</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -4614,17 +4639,17 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.25" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="4" width="5.4140625" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="11.9140625" customWidth="1"/>
+    <col min="1" max="1" width="10.25" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="4" width="5.4140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.9140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -4667,10 +4692,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -4700,15 +4725,15 @@
         <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -4738,15 +4763,15 @@
         <v>6</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -4776,15 +4801,15 @@
         <v>6</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -4814,15 +4839,15 @@
         <v>6</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -4852,15 +4877,15 @@
         <v>6</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -4890,15 +4915,15 @@
         <v>6</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
@@ -4928,15 +4953,15 @@
         <v>6</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
@@ -4966,7 +4991,7 @@
         <v>6</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4980,18 +5005,18 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="3.25" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="11.9140625" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7" style="4" customWidth="1"/>
+    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.9140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5034,13 +5059,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D3" s="2">
         <v>150</v>
@@ -5067,15 +5092,15 @@
         <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -5105,18 +5130,18 @@
         <v>8</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D5" s="2">
         <v>150</v>
@@ -5143,15 +5168,15 @@
         <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -5181,18 +5206,18 @@
         <v>8</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2">
         <v>250</v>
@@ -5219,15 +5244,15 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -5257,18 +5282,18 @@
         <v>8</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D9" s="2">
         <v>150</v>
@@ -5295,18 +5320,18 @@
         <v>8</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2">
         <v>150</v>
@@ -5333,7 +5358,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5347,17 +5372,17 @@
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="3.25" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" customWidth="1"/>
-    <col min="11" max="11" width="3.75" customWidth="1"/>
-    <col min="12" max="12" width="11.9140625" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7" style="4" customWidth="1"/>
+    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.9140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5400,13 +5425,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D3" s="2">
         <v>180</v>
@@ -5433,15 +5458,15 @@
         <v>11</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -5471,15 +5496,15 @@
         <v>9</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -5509,15 +5534,15 @@
         <v>9</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -5547,15 +5572,15 @@
         <v>9</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -5585,15 +5610,15 @@
         <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -5623,15 +5648,15 @@
         <v>9</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
@@ -5661,15 +5686,15 @@
         <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
@@ -5699,7 +5724,7 @@
         <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\Github\newdodge\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\newdodge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCC8591-66F2-43A9-AD3A-33A39F28F3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E91A70-2F98-45B7-B1BE-295C2E7D6CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,12 @@
     <sheet name="爆走ボーイズ" sheetId="5" r:id="rId5"/>
     <sheet name="ドスコイズ" sheetId="6" r:id="rId6"/>
     <sheet name="アイアンガーズ" sheetId="7" r:id="rId7"/>
-    <sheet name="日の丸ボンバーズ" sheetId="8" r:id="rId8"/>
-    <sheet name="くいだおレンジャーズ" sheetId="9" r:id="rId9"/>
+    <sheet name="くいだおレンジャーズ" sheetId="9" r:id="rId8"/>
+    <sheet name="日の丸ボンバーズ" sheetId="8" r:id="rId9"/>
     <sheet name="アメリカンビッグボールズ" sheetId="10" r:id="rId10"/>
     <sheet name="ゼンマイギアーズ" sheetId="11" r:id="rId11"/>
-    <sheet name="アークマーズ" sheetId="12" r:id="rId12"/>
-    <sheet name="ギャラクタコーズ" sheetId="13" r:id="rId13"/>
+    <sheet name="ギャラクタコーズ" sheetId="13" r:id="rId12"/>
+    <sheet name="アークマーズ" sheetId="12" r:id="rId13"/>
     <sheet name="ブレイバーズ" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="0" refMode="R1C1"/>
@@ -1100,7 +1100,7 @@
   <cols>
     <col min="1" max="2" width="8.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="7" style="4" customWidth="1"/>
-    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.08203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="7" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
     <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
@@ -1160,7 +1160,7 @@
         <v>98</v>
       </c>
       <c r="D3" s="2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -1198,7 +1198,7 @@
         <v>77</v>
       </c>
       <c r="D4" s="2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -1236,7 +1236,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="2">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="E5" s="2">
         <v>150</v>
@@ -1274,7 +1274,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="E6" s="2">
         <v>100</v>
@@ -1312,7 +1312,7 @@
         <v>67</v>
       </c>
       <c r="D7" s="2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
@@ -1350,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E8" s="2">
         <v>100</v>
@@ -1388,7 +1388,7 @@
         <v>77</v>
       </c>
       <c r="D9" s="2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="E9" s="2">
         <v>100</v>
@@ -1426,7 +1426,7 @@
         <v>98</v>
       </c>
       <c r="D10" s="2">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="E10" s="2">
         <v>100</v>
@@ -1467,7 +1467,7 @@
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="7" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
     <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
@@ -1531,7 +1531,7 @@
         <v>200</v>
       </c>
       <c r="F3" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2">
         <v>8</v>
@@ -1543,10 +1543,10 @@
         <v>14</v>
       </c>
       <c r="J3" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K3" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>125</v>
@@ -1567,10 +1567,10 @@
         <v>200</v>
       </c>
       <c r="F4" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2">
         <v>6</v>
@@ -1579,10 +1579,10 @@
         <v>11</v>
       </c>
       <c r="J4" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>127</v>
@@ -1603,10 +1603,10 @@
         <v>200</v>
       </c>
       <c r="F5" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2">
         <v>6</v>
@@ -1615,10 +1615,10 @@
         <v>11</v>
       </c>
       <c r="J5" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>127</v>
@@ -1639,10 +1639,10 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2">
         <v>6</v>
@@ -1651,10 +1651,10 @@
         <v>11</v>
       </c>
       <c r="J6" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>127</v>
@@ -1675,10 +1675,10 @@
         <v>200</v>
       </c>
       <c r="F7" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H7" s="2">
         <v>6</v>
@@ -1687,10 +1687,10 @@
         <v>11</v>
       </c>
       <c r="J7" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>127</v>
@@ -1711,10 +1711,10 @@
         <v>200</v>
       </c>
       <c r="F8" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2">
         <v>6</v>
@@ -1723,10 +1723,10 @@
         <v>11</v>
       </c>
       <c r="J8" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>127</v>
@@ -1747,10 +1747,10 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="2">
         <v>6</v>
@@ -1759,10 +1759,10 @@
         <v>11</v>
       </c>
       <c r="J9" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>127</v>
@@ -1783,10 +1783,10 @@
         <v>200</v>
       </c>
       <c r="F10" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10" s="2">
         <v>6</v>
@@ -1795,10 +1795,10 @@
         <v>11</v>
       </c>
       <c r="J10" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>127</v>
@@ -1811,373 +1811,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A2:L10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="11.9140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.08203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="4" customWidth="1"/>
-    <col min="5" max="5" width="7" style="4" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="7" style="4" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
-    <col min="12" max="12" width="19.75" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="2">
-        <v>500</v>
-      </c>
-      <c r="E3" s="2">
-        <v>200</v>
-      </c>
-      <c r="F3" s="2">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2">
-        <v>13</v>
-      </c>
-      <c r="H3" s="2">
-        <v>13</v>
-      </c>
-      <c r="I3" s="2">
-        <v>13</v>
-      </c>
-      <c r="J3" s="2">
-        <v>12</v>
-      </c>
-      <c r="K3" s="2">
-        <v>10</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="2">
-        <v>350</v>
-      </c>
-      <c r="E4" s="2">
-        <v>150</v>
-      </c>
-      <c r="F4" s="2">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2">
-        <v>4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>9</v>
-      </c>
-      <c r="J4" s="2">
-        <v>12</v>
-      </c>
-      <c r="K4" s="2">
-        <v>6</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D5" s="2">
-        <v>270</v>
-      </c>
-      <c r="E5" s="2">
-        <v>150</v>
-      </c>
-      <c r="F5" s="2">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2">
-        <v>11</v>
-      </c>
-      <c r="H5" s="2">
-        <v>9</v>
-      </c>
-      <c r="I5" s="2">
-        <v>12</v>
-      </c>
-      <c r="J5" s="2">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2">
-        <v>7</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D6" s="2">
-        <v>280</v>
-      </c>
-      <c r="E6" s="2">
-        <v>150</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2">
-        <v>12</v>
-      </c>
-      <c r="H6" s="2">
-        <v>8</v>
-      </c>
-      <c r="I6" s="2">
-        <v>14</v>
-      </c>
-      <c r="J6" s="2">
-        <v>13</v>
-      </c>
-      <c r="K6" s="2">
-        <v>16</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="2">
-        <v>250</v>
-      </c>
-      <c r="E7" s="2">
-        <v>150</v>
-      </c>
-      <c r="F7" s="2">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2">
-        <v>10</v>
-      </c>
-      <c r="H7" s="2">
-        <v>9</v>
-      </c>
-      <c r="I7" s="2">
-        <v>13</v>
-      </c>
-      <c r="J7" s="2">
-        <v>6</v>
-      </c>
-      <c r="K7" s="2">
-        <v>8</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="2">
-        <v>130</v>
-      </c>
-      <c r="E8" s="2">
-        <v>135</v>
-      </c>
-      <c r="F8" s="2">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2">
-        <v>13</v>
-      </c>
-      <c r="H8" s="2">
-        <v>13</v>
-      </c>
-      <c r="I8" s="2">
-        <v>12</v>
-      </c>
-      <c r="J8" s="2">
-        <v>6</v>
-      </c>
-      <c r="K8" s="2">
-        <v>16</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D9" s="2">
-        <v>130</v>
-      </c>
-      <c r="E9" s="2">
-        <v>135</v>
-      </c>
-      <c r="F9" s="2">
-        <v>9</v>
-      </c>
-      <c r="G9" s="2">
-        <v>13</v>
-      </c>
-      <c r="H9" s="2">
-        <v>13</v>
-      </c>
-      <c r="I9" s="2">
-        <v>12</v>
-      </c>
-      <c r="J9" s="2">
-        <v>6</v>
-      </c>
-      <c r="K9" s="2">
-        <v>16</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="2">
-        <v>130</v>
-      </c>
-      <c r="E10" s="2">
-        <v>135</v>
-      </c>
-      <c r="F10" s="2">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2">
-        <v>13</v>
-      </c>
-      <c r="H10" s="2">
-        <v>13</v>
-      </c>
-      <c r="I10" s="2">
-        <v>12</v>
-      </c>
-      <c r="J10" s="2">
-        <v>6</v>
-      </c>
-      <c r="K10" s="2">
-        <v>16</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -2245,13 +1878,13 @@
         <v>154</v>
       </c>
       <c r="D3" s="2">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E3" s="2">
         <v>130</v>
       </c>
       <c r="F3" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2">
         <v>8</v>
@@ -2260,10 +1893,10 @@
         <v>20</v>
       </c>
       <c r="I3" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J3" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" s="2">
         <v>8</v>
@@ -2283,7 +1916,7 @@
         <v>154</v>
       </c>
       <c r="D4" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E4" s="2">
         <v>115</v>
@@ -2298,7 +1931,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J4" s="2">
         <v>7</v>
@@ -2321,7 +1954,7 @@
         <v>154</v>
       </c>
       <c r="D5" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E5" s="2">
         <v>115</v>
@@ -2336,7 +1969,7 @@
         <v>16</v>
       </c>
       <c r="I5" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2">
         <v>7</v>
@@ -2359,7 +1992,7 @@
         <v>154</v>
       </c>
       <c r="D6" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E6" s="2">
         <v>120</v>
@@ -2374,7 +2007,7 @@
         <v>16</v>
       </c>
       <c r="I6" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2">
         <v>7</v>
@@ -2397,7 +2030,7 @@
         <v>154</v>
       </c>
       <c r="D7" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E7" s="2">
         <v>115</v>
@@ -2412,7 +2045,7 @@
         <v>16</v>
       </c>
       <c r="I7" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J7" s="2">
         <v>7</v>
@@ -2435,7 +2068,7 @@
         <v>154</v>
       </c>
       <c r="D8" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E8" s="2">
         <v>115</v>
@@ -2450,7 +2083,7 @@
         <v>16</v>
       </c>
       <c r="I8" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8" s="2">
         <v>7</v>
@@ -2473,7 +2106,7 @@
         <v>154</v>
       </c>
       <c r="D9" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E9" s="2">
         <v>120</v>
@@ -2488,7 +2121,7 @@
         <v>16</v>
       </c>
       <c r="I9" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J9" s="2">
         <v>7</v>
@@ -2511,7 +2144,7 @@
         <v>154</v>
       </c>
       <c r="D10" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E10" s="2">
         <v>115</v>
@@ -2526,7 +2159,7 @@
         <v>16</v>
       </c>
       <c r="I10" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" s="2">
         <v>7</v>
@@ -2536,6 +2169,373 @@
       </c>
       <c r="L10" s="1" t="s">
         <v>155</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A2:L10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="11.9140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.08203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="6.5" style="4" customWidth="1"/>
+    <col min="12" max="12" width="19.75" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="2">
+        <v>400</v>
+      </c>
+      <c r="E3" s="2">
+        <v>200</v>
+      </c>
+      <c r="F3" s="2">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2">
+        <v>12</v>
+      </c>
+      <c r="K3" s="2">
+        <v>10</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="2">
+        <v>300</v>
+      </c>
+      <c r="E4" s="2">
+        <v>150</v>
+      </c>
+      <c r="F4" s="2">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9</v>
+      </c>
+      <c r="J4" s="2">
+        <v>14</v>
+      </c>
+      <c r="K4" s="2">
+        <v>6</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="2">
+        <v>230</v>
+      </c>
+      <c r="E5" s="2">
+        <v>150</v>
+      </c>
+      <c r="F5" s="2">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2">
+        <v>11</v>
+      </c>
+      <c r="H5" s="2">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2">
+        <v>11</v>
+      </c>
+      <c r="J5" s="2">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2">
+        <v>7</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="2">
+        <v>250</v>
+      </c>
+      <c r="E6" s="2">
+        <v>150</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
+        <v>12</v>
+      </c>
+      <c r="H6" s="2">
+        <v>8</v>
+      </c>
+      <c r="I6" s="2">
+        <v>13</v>
+      </c>
+      <c r="J6" s="2">
+        <v>13</v>
+      </c>
+      <c r="K6" s="2">
+        <v>16</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="2">
+        <v>230</v>
+      </c>
+      <c r="E7" s="2">
+        <v>150</v>
+      </c>
+      <c r="F7" s="2">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2">
+        <v>9</v>
+      </c>
+      <c r="I7" s="2">
+        <v>11</v>
+      </c>
+      <c r="J7" s="2">
+        <v>6</v>
+      </c>
+      <c r="K7" s="2">
+        <v>8</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="2">
+        <v>200</v>
+      </c>
+      <c r="E8" s="2">
+        <v>135</v>
+      </c>
+      <c r="F8" s="2">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2">
+        <v>13</v>
+      </c>
+      <c r="H8" s="2">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2">
+        <v>11</v>
+      </c>
+      <c r="J8" s="2">
+        <v>6</v>
+      </c>
+      <c r="K8" s="2">
+        <v>16</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="2">
+        <v>200</v>
+      </c>
+      <c r="E9" s="2">
+        <v>135</v>
+      </c>
+      <c r="F9" s="2">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2">
+        <v>13</v>
+      </c>
+      <c r="H9" s="2">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2">
+        <v>11</v>
+      </c>
+      <c r="J9" s="2">
+        <v>6</v>
+      </c>
+      <c r="K9" s="2">
+        <v>16</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="2">
+        <v>200</v>
+      </c>
+      <c r="E10" s="2">
+        <v>135</v>
+      </c>
+      <c r="F10" s="2">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2">
+        <v>11</v>
+      </c>
+      <c r="J10" s="2">
+        <v>6</v>
+      </c>
+      <c r="K10" s="2">
+        <v>16</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2612,13 +2612,13 @@
         <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E3" s="2">
         <v>130</v>
       </c>
       <c r="F3" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2">
         <v>13</v>
@@ -2630,7 +2630,7 @@
         <v>13</v>
       </c>
       <c r="J3" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="2">
         <v>11</v>
@@ -2650,13 +2650,13 @@
         <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E4" s="2">
         <v>115</v>
       </c>
       <c r="F4" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4" s="2">
         <v>7</v>
@@ -2668,7 +2668,7 @@
         <v>8</v>
       </c>
       <c r="J4" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4" s="2">
         <v>8</v>
@@ -2688,13 +2688,13 @@
         <v>21</v>
       </c>
       <c r="D5" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E5" s="2">
         <v>150</v>
       </c>
       <c r="F5" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2">
         <v>8</v>
@@ -2703,7 +2703,7 @@
         <v>8</v>
       </c>
       <c r="I5" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" s="2">
         <v>7</v>
@@ -2726,13 +2726,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="E6" s="2">
         <v>140</v>
       </c>
       <c r="F6" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2">
         <v>9</v>
@@ -2741,10 +2741,10 @@
         <v>9</v>
       </c>
       <c r="I6" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J6" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K6" s="2">
         <v>7</v>
@@ -2764,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="E7" s="2">
         <v>150</v>
@@ -2779,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="I7" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J7" s="2">
         <v>8</v>
@@ -2808,7 +2808,7 @@
         <v>135</v>
       </c>
       <c r="F8" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="2">
         <v>12</v>
@@ -2817,7 +2817,7 @@
         <v>12</v>
       </c>
       <c r="I8" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J8" s="2">
         <v>6</v>
@@ -2840,13 +2840,13 @@
         <v>7</v>
       </c>
       <c r="D9" s="2">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E9" s="2">
         <v>135</v>
       </c>
       <c r="F9" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2">
         <v>18</v>
@@ -2855,13 +2855,13 @@
         <v>18</v>
       </c>
       <c r="I9" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>34</v>
@@ -2878,7 +2878,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="2">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="E10" s="2">
         <v>145</v>
@@ -2887,19 +2887,19 @@
         <v>7</v>
       </c>
       <c r="G10" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2">
         <v>8</v>
       </c>
       <c r="I10" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2">
         <v>7</v>
       </c>
       <c r="K10" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>37</v>
@@ -3541,7 +3541,7 @@
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="7" style="4" customWidth="1"/>
-    <col min="4" max="4" width="2.9140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.58203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="7" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
     <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
@@ -3908,7 +3908,7 @@
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="4" customWidth="1"/>
     <col min="5" max="5" width="7" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
     <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
@@ -4335,7 +4335,7 @@
         <v>77</v>
       </c>
       <c r="D3" s="2">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -4373,7 +4373,7 @@
         <v>77</v>
       </c>
       <c r="D4" s="2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -4411,7 +4411,7 @@
         <v>77</v>
       </c>
       <c r="D5" s="2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="E5" s="2">
         <v>100</v>
@@ -4449,7 +4449,7 @@
         <v>77</v>
       </c>
       <c r="D6" s="2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="E6" s="2">
         <v>100</v>
@@ -4487,7 +4487,7 @@
         <v>77</v>
       </c>
       <c r="D7" s="2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
@@ -4525,7 +4525,7 @@
         <v>77</v>
       </c>
       <c r="D8" s="2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2">
         <v>100</v>
@@ -4563,7 +4563,7 @@
         <v>77</v>
       </c>
       <c r="D9" s="2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2">
         <v>100</v>
@@ -4601,7 +4601,7 @@
         <v>77</v>
       </c>
       <c r="D10" s="2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="E10" s="2">
         <v>100</v>
@@ -4701,7 +4701,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -5001,14 +5001,13 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="7" style="4" customWidth="1"/>
-    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="7" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
     <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
@@ -5059,7 +5058,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>39</v>
@@ -5068,36 +5067,36 @@
         <v>67</v>
       </c>
       <c r="D3" s="2">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E3" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F3" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="2">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2">
+        <v>9</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9</v>
+      </c>
+      <c r="J3" s="2">
+        <v>9</v>
+      </c>
+      <c r="K3" s="2">
         <v>11</v>
       </c>
-      <c r="H3" s="2">
-        <v>9</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8</v>
-      </c>
-      <c r="J3" s="2">
-        <v>8</v>
-      </c>
-      <c r="K3" s="2">
-        <v>8</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>39</v>
@@ -5106,28 +5105,28 @@
         <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G4" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>58</v>
@@ -5135,45 +5134,45 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E5" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="2">
         <v>8</v>
       </c>
       <c r="H5" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>39</v>
@@ -5182,28 +5181,28 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E6" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J6" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K6" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>58</v>
@@ -5211,45 +5210,45 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2">
         <v>9</v>
       </c>
       <c r="I7" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K7" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>45</v>
@@ -5258,28 +5257,28 @@
         <v>14</v>
       </c>
       <c r="D8" s="2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E8" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F8" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J8" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K8" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>58</v>
@@ -5287,37 +5286,37 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H9" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I9" s="2">
         <v>7</v>
       </c>
       <c r="J9" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>58</v>
@@ -5325,37 +5324,37 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E10" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2">
         <v>8</v>
       </c>
       <c r="G10" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H10" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K10" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>58</v>
@@ -5368,13 +5367,14 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A2:L10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="7" style="4" customWidth="1"/>
-    <col min="4" max="4" width="3.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.4140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="7" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="4" customWidth="1"/>
     <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>39</v>
@@ -5434,36 +5434,36 @@
         <v>67</v>
       </c>
       <c r="D3" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E3" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F3" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H3" s="2">
         <v>9</v>
       </c>
       <c r="I3" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>39</v>
@@ -5472,28 +5472,28 @@
         <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E4" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F4" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>58</v>
@@ -5501,45 +5501,45 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="D5" s="2">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E5" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F5" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2">
         <v>8</v>
       </c>
       <c r="H5" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>39</v>
@@ -5548,28 +5548,28 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E6" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F6" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>58</v>
@@ -5577,45 +5577,45 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="E7" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F7" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G7" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" s="2">
         <v>9</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>45</v>
@@ -5624,28 +5624,28 @@
         <v>14</v>
       </c>
       <c r="D8" s="2">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E8" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F8" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G8" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H8" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I8" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>58</v>
@@ -5653,37 +5653,37 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="D9" s="2">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E9" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9" s="2">
         <v>7</v>
       </c>
       <c r="J9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>58</v>
@@ -5691,37 +5691,37 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E10" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F10" s="2">
         <v>8</v>
       </c>
       <c r="G10" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K10" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>58</v>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\newdodge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E91A70-2F98-45B7-B1BE-295C2E7D6CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2D5BC2-16A9-4868-9B6F-5F80BC1C21B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3650" yWindow="5270" windowWidth="30970" windowHeight="13040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="1" r:id="rId1"/>
@@ -820,7 +820,7 @@
     <col min="7" max="7" width="6.9140625" style="4" customWidth="1"/>
     <col min="8" max="8" width="7" style="4" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="10.58203125" style="4" customWidth="1"/>
     <col min="11" max="11" width="19.08203125" style="4" customWidth="1"/>
     <col min="12" max="12" width="10.25" style="4" customWidth="1"/>
   </cols>
@@ -874,7 +874,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -902,7 +902,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -930,7 +930,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E5" s="2">
         <v>100</v>
@@ -958,7 +958,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E6" s="2">
         <v>100</v>
@@ -986,7 +986,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
@@ -1014,7 +1014,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2">
         <v>100</v>
@@ -1042,7 +1042,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2">
         <v>100</v>
@@ -1070,7 +1070,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2">
         <v>100</v>
@@ -2979,7 +2979,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -3007,7 +3007,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -3035,7 +3035,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E5" s="2">
         <v>100</v>
@@ -3063,7 +3063,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E6" s="2">
         <v>100</v>
@@ -3091,7 +3091,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
@@ -3119,7 +3119,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2">
         <v>100</v>
@@ -3147,7 +3147,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2">
         <v>100</v>
@@ -3968,7 +3968,7 @@
         <v>67</v>
       </c>
       <c r="D3" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E3" s="2">
         <v>100</v>
@@ -4006,7 +4006,7 @@
         <v>67</v>
       </c>
       <c r="D4" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
@@ -4044,7 +4044,7 @@
         <v>67</v>
       </c>
       <c r="D5" s="2">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="E5" s="2">
         <v>100</v>
@@ -4082,7 +4082,7 @@
         <v>67</v>
       </c>
       <c r="D6" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2">
         <v>100</v>
@@ -4120,7 +4120,7 @@
         <v>67</v>
       </c>
       <c r="D7" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2">
         <v>100</v>
@@ -4158,7 +4158,7 @@
         <v>67</v>
       </c>
       <c r="D8" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E8" s="2">
         <v>100</v>
@@ -4196,7 +4196,7 @@
         <v>67</v>
       </c>
       <c r="D9" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2">
         <v>100</v>
@@ -4234,7 +4234,7 @@
         <v>67</v>
       </c>
       <c r="D10" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2">
         <v>100</v>

--- a/data/status.xlsx
+++ b/data/status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\newdodge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F68CA6-51EC-4C8C-8F55-41018288B361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC943FB-1B7B-4506-B85C-59CCD5D0F3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3650" yWindow="5270" windowWidth="30970" windowHeight="13040" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3650" yWindow="5270" windowWidth="30970" windowHeight="13040" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ブルースターズ" sheetId="1" r:id="rId1"/>
@@ -2342,7 +2342,7 @@
         <v>104</v>
       </c>
       <c r="D3" s="2">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E3" s="2">
         <v>200</v>
@@ -2357,10 +2357,10 @@
         <v>13</v>
       </c>
       <c r="I3" s="2">
+        <v>14</v>
+      </c>
+      <c r="J3" s="2">
         <v>13</v>
-      </c>
-      <c r="J3" s="2">
-        <v>12</v>
       </c>
       <c r="K3" s="2">
         <v>10</v>
@@ -2386,7 +2386,7 @@
         <v>150</v>
       </c>
       <c r="F4" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2">
         <v>5</v>
@@ -2418,7 +2418,7 @@
         <v>109</v>
       </c>
       <c r="D5" s="2">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E5" s="2">
         <v>150</v>
@@ -2427,10 +2427,10 @@
         <v>12</v>
       </c>
       <c r="G5" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2">
         <v>11</v>
@@ -2439,7 +2439,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>110</v>
@@ -2715,7 +2715,7 @@
         <v>130</v>
       </c>
       <c r="F3" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2">
         <v>13</v>
@@ -2747,13 +2747,13 @@
         <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E4" s="2">
         <v>115</v>
       </c>
       <c r="F4" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G4" s="2">
         <v>7</v>
@@ -2785,7 +2785,7 @@
         <v>129</v>
       </c>
       <c r="D5" s="2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E5" s="2">
         <v>150</v>
@@ -2952,7 +2952,7 @@
         <v>20</v>
       </c>
       <c r="I9" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J9" s="2">
         <v>9</v>
